--- a/output/pdf_financials_xlsx/GASX.xlsx
+++ b/output/pdf_financials_xlsx/GASX.xlsx
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>574554</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>1007799</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>76925</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
@@ -890,16 +890,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>0.315289</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>1.973953</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>6.402007</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>11.77373</v>
       </c>
     </row>
     <row r="10">
@@ -7056,13 +7056,13 @@
         <v>-0.024624</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.023114</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.012821</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000902</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -46984,7 +46984,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -49462,7 +49466,11 @@
           <t>Exploration and evaluation expense</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -51754,7 +51762,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
           <t>-</t>
@@ -51791,13 +51803,13 @@
         </is>
       </c>
       <c r="L459" s="5" t="n">
-        <v>-574554</v>
+        <v>574554</v>
       </c>
       <c r="M459" s="5" t="n">
-        <v>-1007799</v>
+        <v>1007799</v>
       </c>
       <c r="N459" s="5" t="n">
-        <v>-76925</v>
+        <v>76925</v>
       </c>
       <c r="O459" t="inlineStr">
         <is>
@@ -51810,16 +51822,16 @@
         </is>
       </c>
       <c r="Q459" s="5" t="n">
-        <v>-0.315289</v>
+        <v>0.315289</v>
       </c>
       <c r="R459" s="5" t="n">
-        <v>-1.973953</v>
+        <v>1.973953</v>
       </c>
       <c r="S459" s="5" t="n">
-        <v>-6.402007</v>
+        <v>6.402007</v>
       </c>
       <c r="T459" s="5" t="n">
-        <v>-11.77373</v>
+        <v>11.77373</v>
       </c>
     </row>
     <row r="460">

--- a/output/pdf_financials_xlsx/GASX.xlsx
+++ b/output/pdf_financials_xlsx/GASX.xlsx
@@ -1057,22 +1057,22 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.100775</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.08237700000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.273892</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.7733989999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.523733</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.25006</v>
       </c>
     </row>
     <row r="13">
@@ -1978,22 +1978,22 @@
         <v>-2697356</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-23.700405</v>
+        <v>-23.59963</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.714447</v>
+        <v>-6.63207</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.567507</v>
+        <v>-10.293615</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-16.530145</v>
+        <v>-15.756746</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-54.063087</v>
+        <v>-53.539354</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-35.290296</v>
+        <v>-35.040236</v>
       </c>
     </row>
     <row r="28">
@@ -2090,22 +2090,22 @@
         <v>-2183315</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-23.683157</v>
+        <v>-23.582382</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.707679</v>
+        <v>-6.625302</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-9.546938000000001</v>
+        <v>-9.273046000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-10.999434</v>
+        <v>-10.226035</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-44.58972</v>
+        <v>-44.065987</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-23.641753</v>
+        <v>-23.391693</v>
       </c>
     </row>
     <row r="30">
@@ -53726,7 +53726,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -57528,7 +57528,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -59348,7 +59348,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">

--- a/output/pdf_financials_xlsx/GASX.xlsx
+++ b/output/pdf_financials_xlsx/GASX.xlsx
@@ -1106,28 +1106,28 @@
         <v>-0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-25934</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-191759</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.154222</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.254792</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-4.642056</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-20.18784</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-33.867366</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>-50.69047</v>
       </c>
     </row>
     <row r="14">
@@ -1972,28 +1972,28 @@
         <v>-17065695</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-65067125</v>
+        <v>-65041191</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2697356</v>
+        <v>-2505597</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-23.59963</v>
+        <v>-22.445408</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.63207</v>
+        <v>-5.377278</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.293615</v>
+        <v>-5.651559</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-15.756746</v>
+        <v>4.431094</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-53.539354</v>
+        <v>-19.671988</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-35.040236</v>
+        <v>15.650234</v>
       </c>
     </row>
     <row r="28">
@@ -2084,28 +2084,28 @@
         <v>-16107607</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-63529576</v>
+        <v>-63503642</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2183315</v>
+        <v>-1991556</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-23.582382</v>
+        <v>-22.42816</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.625302</v>
+        <v>-5.37051</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-9.273046000000001</v>
+        <v>-4.63099</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-10.226035</v>
+        <v>9.961805</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-44.065987</v>
+        <v>-10.198621</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-23.391693</v>
+        <v>27.298777</v>
       </c>
     </row>
     <row r="30">
@@ -2153,10 +2153,10 @@
         <v>-561.7530904497552</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1210.485584588604</v>
+        <v>-1209.991440992388</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-153.7838180499109</v>
+        <v>-140.2770949405873</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -6726,10 +6726,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -46890,7 +46890,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -52504,7 +52508,11 @@
           <t>Net finance expense (Note 19)</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -54672,7 +54680,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -55146,7 +55158,11 @@
           <t>Net finance expense (Note 19)</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -56476,7 +56492,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
           <t>-</t>
@@ -56950,7 +56970,11 @@
           <t>Net finance expense (Note 19)</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -58004,7 +58028,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>-</t>
@@ -58482,7 +58510,11 @@
           <t>Net finance expense (Note 16)</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E530" t="inlineStr">
         <is>
           <t>-</t>
@@ -59726,7 +59758,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E543" t="inlineStr">
         <is>
           <t>-</t>
@@ -60102,7 +60138,11 @@
           <t>Net finance expense (Note 14)</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -61332,7 +61372,11 @@
           <t>Total net finance expense</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -62274,7 +62318,11 @@
           <t>Net finance expense (Note 22)</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E570" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GASX.xlsx
+++ b/output/pdf_financials_xlsx/GASX.xlsx
@@ -1325,10 +1325,10 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>3058518</v>
+        <v>-1313001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3831850</v>
+        <v>-3831850</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1340,16 +1340,16 @@
         <v>-0</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.599349</v>
+        <v>-0.599349</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0.147431</v>
+        <v>0.364506</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.364506</v>
+        <v>-0.364506</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>11.208462</v>
+        <v>-11.208462</v>
       </c>
     </row>
     <row r="18">
@@ -1546,17 +1546,19 @@
       <c r="E20" s="3" t="n">
         <v>-0.027628</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-0.028098</v>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.042086</v>
+        <v>-0.002865</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-523441</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-14007177</v>
+        <v>-15752694</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-61235275</v>
@@ -1565,7 +1567,7 @@
         <v>-2697356</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-23.700405</v>
+        <v>-22.009042</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-6.714447</v>
@@ -1602,13 +1604,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.028509</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.039221</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-0.001494</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -2219,7 +2221,7 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-17.92202427149905</v>
+        <v>-7.693803270244781</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-5.889072246545394</v>
@@ -2237,7 +2239,7 @@
         <v>-5.671621509216886</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.891891752915658</v>
+        <v>-2.205098624361734</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0.6742234308595807</v>
@@ -4072,31 +4074,31 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>16585780</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>11851187</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>3187015</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>3.177873</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>2.615205</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>9.685105999999999</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>12.112608</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>14.915586</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>33.645856</v>
       </c>
     </row>
     <row r="65">
@@ -4417,16 +4419,16 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>2.776384</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>7.30859</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>6.289994</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>16.563276</v>
       </c>
     </row>
     <row r="71">
@@ -4472,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>2.776384</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>7.30859</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>6.289994</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>16.563276</v>
       </c>
     </row>
     <row r="72">
@@ -4698,10 +4700,10 @@
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>16.387641</v>
+        <v>10.097647</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>103.538851</v>
+        <v>86.97557500000001</v>
       </c>
     </row>
     <row r="76">
@@ -4877,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>21.480395</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>16.52488</v>
       </c>
       <c r="P78" s="3" t="n">
         <v>0</v>
@@ -4932,10 +4934,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>21.480395</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>16.52488</v>
       </c>
       <c r="P79" s="3" t="n">
         <v>0</v>
@@ -5010,25 +5012,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" s="3" t="n">
+        <v>1.564293755594818</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>2.361771742775398</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.1403291316951561</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.7472805450964992</v>
       </c>
     </row>
     <row r="81">
@@ -6014,10 +6008,10 @@
         <v>-0.027628</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.028098</v>
+        <v>-0.028608</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-0.042086</v>
+        <v>-0.002865</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>-523441</v>
@@ -9752,7 +9746,11 @@
           <t>Current portion of lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10310,7 +10308,11 @@
           <t>Non-current portion of lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -12538,7 +12540,11 @@
           <t>Non‐current portion of lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13976,7 +13982,11 @@
           <t>Lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -25622,7 +25632,11 @@
           <t>Deferred income tax recovery (Note 21)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -27062,7 +27076,11 @@
           <t>Proceeds on private placement</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -27158,7 +27176,11 @@
           <t>Transaction costs paid on private placement</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32506,7 +32528,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -39010,7 +39036,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -41126,7 +41156,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -41698,7 +41732,11 @@
           <t>Deferred income tax expense/(recovery) (Note 17)</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -44080,7 +44118,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -46046,7 +46088,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -53082,7 +53128,11 @@
           <t>Current income tax recovery (Note 21)</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -53178,7 +53228,11 @@
           <t>Deferred income tax recovery (Note 21)</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -55546,7 +55600,11 @@
           <t>Current income tax recovery (expense) (Note 21)</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -57358,7 +57416,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
@@ -60428,7 +60490,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
           <t>-</t>
@@ -63948,7 +64014,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
           <t>-</t>
@@ -64042,7 +64112,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
           <t>-</t>
@@ -64810,7 +64884,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E596" t="inlineStr">
         <is>
           <t>-</t>
@@ -65764,7 +65842,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E606" t="inlineStr">
         <is>
           <t>-</t>
@@ -65858,7 +65940,11 @@
           <t>Loss from discontinued operations (Note 11)</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>
@@ -68688,7 +68774,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E637" t="inlineStr">
         <is>
           <t>-</t>
@@ -69444,7 +69534,11 @@
           <t>Net income from discontinued operat - - -</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E645" t="inlineStr">
         <is>
           <t>-</t>
@@ -70108,7 +70202,11 @@
           <t>Net loss from discontinued operation - - -</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E652" t="inlineStr">
         <is>
           <t>-</t>
